--- a/Fitter/Muons/2018/GoldID/sfs_mcol.xlsx
+++ b/Fitter/Muons/2018/GoldID/sfs_mcol.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/neilj/Desktop/python1/Physics/KU_CMS_TnP/Fitter/Muons/2018/GoldID/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/neilj/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F4294C7-DC50-0243-BACB-0BE6C00C110B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{121D02B6-7BE5-CC47-94DE-445FA84BE35A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33320" yWindow="7880" windowWidth="17620" windowHeight="14380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="34200" windowHeight="21460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ScaleFactors" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="23">
   <si>
     <t>Type</t>
   </si>
@@ -1336,6 +1336,9 @@
       <c r="K27">
         <v>5.0000000000000001E-3</v>
       </c>
+      <c r="L27" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
@@ -1400,6 +1403,9 @@
       <c r="K29">
         <v>5.0000000000000001E-3</v>
       </c>
+      <c r="L29" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
@@ -1464,6 +1470,9 @@
       <c r="K31">
         <v>5.0000000000000001E-3</v>
       </c>
+      <c r="L31" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
@@ -1494,7 +1503,7 @@
         <v>8.8000000000000005E-3</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>18</v>
       </c>
@@ -1528,8 +1537,11 @@
       <c r="K33">
         <v>5.0000000000000001E-3</v>
       </c>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L33" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>12</v>
       </c>
@@ -1558,7 +1570,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>18</v>
       </c>
@@ -1592,8 +1604,11 @@
       <c r="K35">
         <v>5.0000000000000001E-3</v>
       </c>
-    </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L35" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>12</v>
       </c>
@@ -1622,7 +1637,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>18</v>
       </c>
@@ -1656,8 +1671,11 @@
       <c r="K37">
         <v>5.0000000000000001E-3</v>
       </c>
-    </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L37" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>12</v>
       </c>
@@ -1686,7 +1704,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>18</v>
       </c>
@@ -1720,8 +1738,11 @@
       <c r="K39">
         <v>5.0000000000000001E-3</v>
       </c>
-    </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L39" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>12</v>
       </c>
@@ -1750,7 +1771,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>18</v>
       </c>
@@ -1783,6 +1804,9 @@
       </c>
       <c r="K41">
         <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="L41" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
